--- a/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_PH2_FEB26.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_PH2_FEB26.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.mohler_cn\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.mohler_cn\Projects\ITM\itm-evaluation-dashboard\dashboard-ui\src\components\Research\variables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4E433A-D47B-4836-9BB8-6E113224D043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62122F91-FCD2-4C8B-BBAD-266F3BE991D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1455" yWindow="0" windowWidth="26400" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RQ8" sheetId="1" r:id="rId1"/>
@@ -424,9 +424,6 @@
     <t>Patient A or Patient B</t>
   </si>
   <si>
-    <t>5 = remain in place; 4 = ask for verbal clarification; 3 = attempt to drag patient inside; 2 = express vocal concern but go anyway; 1 = ignore warning</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
@@ -535,82 +532,85 @@
     <t>5 = run for cover and wait for all clear; 4 = stop and stare; 3 = attempt to drag patients inside; 2 = express vocal concern but keep treating; 1 = ignore drones</t>
   </si>
   <si>
+    <t>Desert Probe_PS1_Actions</t>
+  </si>
+  <si>
+    <t>Desert Probe_PS2_Actions</t>
+  </si>
+  <si>
+    <t>List of moderator buttons selected in response to initial PS inject</t>
+  </si>
+  <si>
+    <t>List of moderator buttons selected in response to drone</t>
+  </si>
+  <si>
+    <t>Affiliation Focus KDMA measurement from simulation; intercept term (1 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
+  </si>
+  <si>
+    <t>Affiliation Focus KDMA measurement from OW sim; medical urgency term (2 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
+  </si>
+  <si>
+    <t>Affiliation Focus KDMA measurement from OW sim; attribute term (3 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
+  </si>
+  <si>
+    <t>Merit Focus KDMA measurement from OW sim; intercept term (1 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
+  </si>
+  <si>
+    <t>Merit Focus KDMA measurement from OW sim; medical urgency term (2 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
+  </si>
+  <si>
+    <t>Merit Focus KDMA measurement from OW sim; attribute term (3 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
+  </si>
+  <si>
+    <t>Affiliation Focus KDMA measurement from OW sim; medical urgency term (2 of 3 terms in regression approach);TA1 server calculation via probe matcher</t>
+  </si>
+  <si>
+    <t>ADEPT server</t>
+  </si>
+  <si>
+    <t>Alignment between MF_text and MF_urban</t>
+  </si>
+  <si>
+    <t>AF Alignment_Urban</t>
+  </si>
+  <si>
+    <t>MF Alignment_Urban</t>
+  </si>
+  <si>
+    <t>Alignment between AF_text and AF_urban</t>
+  </si>
+  <si>
+    <t>MF Alignment_Desert</t>
+  </si>
+  <si>
+    <t>AF Alignment_Desert</t>
+  </si>
+  <si>
+    <t>Alignment between AF_text and AF_desert</t>
+  </si>
+  <si>
+    <t>Alignment between MF_text and MF_desert</t>
+  </si>
+  <si>
+    <t>Desert Spawn_location</t>
+  </si>
+  <si>
+    <t>Urban Spawn_location</t>
+  </si>
+  <si>
+    <t>The even PIDs (value of 0) spawn inside the big building; the odd PIDs (value of 1) spawn inside the small building.</t>
+  </si>
+  <si>
+    <t>The even PIDs (value of 0) spawn inside the office building; the odd PIDs (value of 1) spawn inside the recycling center.</t>
+  </si>
+  <si>
+    <t>0 or 1</t>
+  </si>
+  <si>
+    <t>4 = Remain in place; 3 = Verbal Response / Ask for clarification; 2 = Drag patient inside; 1 =Ignore warning and approach patient</t>
+  </si>
+  <si>
     <t>5 = remain in place; 4 = verbal concern but remain in place; 3 = attempt to drag patient inside; 2 = express vocal concern but go anyway; 1 = ignore warning</t>
-  </si>
-  <si>
-    <t>Desert Probe_PS1_Actions</t>
-  </si>
-  <si>
-    <t>Desert Probe_PS2_Actions</t>
-  </si>
-  <si>
-    <t>List of moderator buttons selected in response to initial PS inject</t>
-  </si>
-  <si>
-    <t>List of moderator buttons selected in response to drone</t>
-  </si>
-  <si>
-    <t>Affiliation Focus KDMA measurement from simulation; intercept term (1 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
-  </si>
-  <si>
-    <t>Affiliation Focus KDMA measurement from OW sim; medical urgency term (2 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
-  </si>
-  <si>
-    <t>Affiliation Focus KDMA measurement from OW sim; attribute term (3 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
-  </si>
-  <si>
-    <t>Merit Focus KDMA measurement from OW sim; intercept term (1 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
-  </si>
-  <si>
-    <t>Merit Focus KDMA measurement from OW sim; medical urgency term (2 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
-  </si>
-  <si>
-    <t>Merit Focus KDMA measurement from OW sim; attribute term (3 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
-  </si>
-  <si>
-    <t>Affiliation Focus KDMA measurement from OW sim; medical urgency term (2 of 3 terms in regression approach);TA1 server calculation via probe matcher</t>
-  </si>
-  <si>
-    <t>ADEPT server</t>
-  </si>
-  <si>
-    <t>Alignment between MF_text and MF_urban</t>
-  </si>
-  <si>
-    <t>AF Alignment_Urban</t>
-  </si>
-  <si>
-    <t>MF Alignment_Urban</t>
-  </si>
-  <si>
-    <t>Alignment between AF_text and AF_urban</t>
-  </si>
-  <si>
-    <t>MF Alignment_Desert</t>
-  </si>
-  <si>
-    <t>AF Alignment_Desert</t>
-  </si>
-  <si>
-    <t>Alignment between AF_text and AF_desert</t>
-  </si>
-  <si>
-    <t>Alignment between MF_text and MF_desert</t>
-  </si>
-  <si>
-    <t>Desert Spawn_location</t>
-  </si>
-  <si>
-    <t>Urban Spawn_location</t>
-  </si>
-  <si>
-    <t>The even PIDs (value of 0) spawn inside the big building; the odd PIDs (value of 1) spawn inside the small building.</t>
-  </si>
-  <si>
-    <t>The even PIDs (value of 0) spawn inside the office building; the odd PIDs (value of 1) spawn inside the recycling center.</t>
-  </si>
-  <si>
-    <t>0 or 1</t>
   </si>
 </sst>
 </file>
@@ -1149,10 +1149,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F1" s="19" t="s">
         <v>3</v>
@@ -1185,10 +1185,10 @@
         <v>12</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Q1" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R1" s="17" t="s">
         <v>13</v>
@@ -1398,16 +1398,16 @@
         <v>81</v>
       </c>
       <c r="CI1" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="CJ1" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="CK1" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="CL1" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:90" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1670,16 +1670,16 @@
         <v>87</v>
       </c>
       <c r="CI2" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="CJ2" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="CK2" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="CL2" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:90" s="7" customFormat="1" ht="208.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1693,10 +1693,10 @@
         <v>90</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F3" s="19" t="s">
         <v>91</v>
@@ -1726,13 +1726,13 @@
         <v>93</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P3" s="19" t="s">
         <v>93</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R3" s="17" t="s">
         <v>94</v>
@@ -1906,52 +1906,52 @@
         <v>124</v>
       </c>
       <c r="BW3" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="BX3" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="BY3" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="BX3" s="24" t="s">
+      <c r="BZ3" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="BY3" s="24" t="s">
+      <c r="CA3" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="BZ3" s="24" t="s">
+      <c r="CB3" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="CA3" s="24" t="s">
+      <c r="CC3" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="CD3" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="CB3" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="CC3" s="24" t="s">
+      <c r="CE3" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="CD3" s="24" t="s">
+      <c r="CF3" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="CG3" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="CH3" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="CI3" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="CJ3" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK3" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="CE3" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="CF3" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="CG3" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="CH3" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="CI3" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="CJ3" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="CK3" s="12" t="s">
-        <v>178</v>
-      </c>
       <c r="CL3" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:90" s="7" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1963,10 +1963,10 @@
         <v>126</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F4" s="19" t="s">
         <v>127</v>
@@ -1993,16 +1993,16 @@
         <v>127</v>
       </c>
       <c r="N4" s="19" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="O4" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P4" s="19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R4" s="17" t="s">
         <v>127</v>
@@ -2029,115 +2029,115 @@
         <v>127</v>
       </c>
       <c r="Z4" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="AA4" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="AA4" s="19" t="s">
+      <c r="AB4" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="AB4" s="19" t="s">
+      <c r="AC4" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="AC4" s="19" t="s">
+      <c r="AD4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE4" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG4" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="AD4" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="AE4" s="17" t="s">
+      <c r="AH4" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="AI4" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="AJ4" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK4" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="AF4" s="17" t="s">
+      <c r="AL4" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM4" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="AG4" s="19" t="s">
+      <c r="AN4" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="AH4" s="19" t="s">
+      <c r="AO4" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="AP4" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ4" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR4" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="AS4" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="AT4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AU4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AV4" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW4" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="AI4" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="AJ4" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="AK4" s="19" t="s">
+      <c r="AX4" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY4" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="AZ4" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="AL4" s="19" t="s">
+      <c r="BA4" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB4" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="AM4" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN4" s="19" t="s">
+      <c r="BC4" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="BD4" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE4" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF4" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="BG4" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="AO4" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="AP4" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="AQ4" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="AR4" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="AS4" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="AT4" s="17" t="s">
+      <c r="BH4" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="AU4" s="17" t="s">
+      <c r="BI4" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="AV4" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="AW4" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="AX4" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="AY4" s="19" t="s">
+      <c r="BJ4" s="17" t="s">
         <v>135</v>
-      </c>
-      <c r="AZ4" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="BA4" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="BB4" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC4" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="BD4" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="BE4" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="BF4" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="BG4" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="BH4" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="BI4" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="BJ4" s="17" t="s">
-        <v>136</v>
       </c>
       <c r="BK4" s="15"/>
       <c r="BL4" s="15"/>
@@ -2243,136 +2243,136 @@
   <sheetData>
     <row r="1" spans="1:6" s="11" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2"/>
@@ -10329,136 +10329,136 @@
   <sheetData>
     <row r="1" spans="1:6" s="11" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2"/>

--- a/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_PH2_FEB26.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_PH2_FEB26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.mohler_cn\Projects\ITM\itm-evaluation-dashboard\dashboard-ui\src\components\Research\variables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62122F91-FCD2-4C8B-BBAD-266F3BE991D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E843824C-3A63-40FC-B31C-C6622C163E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1455" yWindow="0" windowWidth="26400" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RQ8" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="196">
   <si>
     <t>Variables</t>
   </si>
@@ -611,6 +611,21 @@
   </si>
   <si>
     <t>5 = remain in place; 4 = verbal concern but remain in place; 3 = attempt to drag patient inside; 2 = express vocal concern but go anyway; 1 = ignore warning</t>
+  </si>
+  <si>
+    <t>Desert Patient{N}_dragged</t>
+  </si>
+  <si>
+    <t>Whether patient {N} was dragged at any point or not</t>
+  </si>
+  <si>
+    <t>Yes/No</t>
+  </si>
+  <si>
+    <t>Urban Patient{N}_dragged</t>
+  </si>
+  <si>
+    <t>0 = No evac, 1 = Round 1 evac, 2 = Round 2 evac</t>
   </si>
 </sst>
 </file>
@@ -1096,7 +1111,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:CL6"/>
+  <dimension ref="A1:CN6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="16.7109375" style="6" bestFit="1" customWidth="1"/>
@@ -1114,31 +1129,31 @@
     <col min="37" max="41" width="13" style="20" bestFit="1" customWidth="1"/>
     <col min="42" max="45" width="16.7109375" style="18" bestFit="1" customWidth="1"/>
     <col min="46" max="50" width="13" style="18" bestFit="1" customWidth="1"/>
-    <col min="51" max="56" width="13" style="20" bestFit="1" customWidth="1"/>
-    <col min="57" max="62" width="13" style="18" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="87.7109375" style="16" customWidth="1"/>
-    <col min="64" max="65" width="73" style="16" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="38.5703125" style="14" customWidth="1"/>
-    <col min="67" max="67" width="34.7109375" style="14" customWidth="1"/>
-    <col min="68" max="68" width="73" style="16" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="32.5703125" style="14" customWidth="1"/>
-    <col min="70" max="74" width="32.28515625" style="14" customWidth="1"/>
-    <col min="75" max="75" width="87.7109375" style="25" customWidth="1"/>
-    <col min="76" max="77" width="73" style="25" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="38.5703125" style="23" customWidth="1"/>
-    <col min="79" max="79" width="34.7109375" style="23" customWidth="1"/>
-    <col min="80" max="80" width="73" style="25" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="87.7109375" style="25" customWidth="1"/>
-    <col min="82" max="83" width="73" style="25" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="38.5703125" style="23" customWidth="1"/>
-    <col min="85" max="85" width="34.7109375" style="23" customWidth="1"/>
-    <col min="86" max="86" width="73" style="25" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="14.7109375" style="13" customWidth="1"/>
-    <col min="88" max="88" width="15.28515625" style="13" customWidth="1"/>
-    <col min="89" max="90" width="9.140625" style="13"/>
+    <col min="51" max="57" width="13" style="20" bestFit="1" customWidth="1"/>
+    <col min="58" max="64" width="13" style="18" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="87.7109375" style="16" customWidth="1"/>
+    <col min="66" max="67" width="73" style="16" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="38.5703125" style="14" customWidth="1"/>
+    <col min="69" max="69" width="34.7109375" style="14" customWidth="1"/>
+    <col min="70" max="70" width="73" style="16" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="32.5703125" style="14" customWidth="1"/>
+    <col min="72" max="76" width="32.28515625" style="14" customWidth="1"/>
+    <col min="77" max="77" width="87.7109375" style="25" customWidth="1"/>
+    <col min="78" max="79" width="73" style="25" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="38.5703125" style="23" customWidth="1"/>
+    <col min="81" max="81" width="34.7109375" style="23" customWidth="1"/>
+    <col min="82" max="82" width="73" style="25" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="87.7109375" style="25" customWidth="1"/>
+    <col min="84" max="85" width="73" style="25" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="38.5703125" style="23" customWidth="1"/>
+    <col min="87" max="87" width="34.7109375" style="23" customWidth="1"/>
+    <col min="88" max="88" width="73" style="25" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="14.7109375" style="13" customWidth="1"/>
+    <col min="90" max="90" width="15.28515625" style="13" customWidth="1"/>
+    <col min="91" max="92" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:90" s="7" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:92" s="7" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1307,110 +1322,116 @@
       <c r="BD1" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="BE1" s="17" t="s">
+      <c r="BE1" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="BF1" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="BF1" s="17" t="s">
+      <c r="BG1" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="BG1" s="17" t="s">
+      <c r="BH1" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="BH1" s="17" t="s">
+      <c r="BI1" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="BI1" s="17" t="s">
+      <c r="BJ1" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="BJ1" s="17" t="s">
+      <c r="BK1" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="BK1" s="14" t="s">
+      <c r="BL1" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="BM1" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="BL1" s="14" t="s">
+      <c r="BN1" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="BM1" s="14" t="s">
+      <c r="BO1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="BN1" s="14" t="s">
+      <c r="BP1" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="BO1" s="14" t="s">
+      <c r="BQ1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="BP1" s="14" t="s">
+      <c r="BR1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="BQ1" s="14" t="s">
+      <c r="BS1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="BR1" s="14" t="s">
+      <c r="BT1" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="BS1" s="14" t="s">
+      <c r="BU1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="BT1" s="14" t="s">
+      <c r="BV1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="BU1" s="14" t="s">
+      <c r="BW1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="BV1" s="14" t="s">
+      <c r="BX1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="BW1" s="23" t="s">
+      <c r="BY1" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="BX1" s="23" t="s">
+      <c r="BZ1" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="BY1" s="23" t="s">
+      <c r="CA1" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="BZ1" s="23" t="s">
+      <c r="CB1" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="CA1" s="23" t="s">
+      <c r="CC1" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="CB1" s="23" t="s">
+      <c r="CD1" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="CC1" s="23" t="s">
+      <c r="CE1" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="CD1" s="23" t="s">
+      <c r="CF1" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="CE1" s="23" t="s">
+      <c r="CG1" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="CF1" s="23" t="s">
+      <c r="CH1" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="CG1" s="23" t="s">
+      <c r="CI1" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="CH1" s="23" t="s">
+      <c r="CJ1" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="CI1" s="12" t="s">
+      <c r="CK1" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="CJ1" s="12" t="s">
+      <c r="CL1" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="CK1" s="12" t="s">
+      <c r="CM1" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="CL1" s="12" t="s">
+      <c r="CN1" s="12" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:90" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:92" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>82</v>
       </c>
@@ -1579,7 +1600,7 @@
       <c r="BD2" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="BE2" s="17" t="s">
+      <c r="BE2" s="19" t="s">
         <v>85</v>
       </c>
       <c r="BF2" s="17" t="s">
@@ -1597,11 +1618,11 @@
       <c r="BJ2" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="BK2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="BL2" s="15" t="s">
-        <v>86</v>
+      <c r="BK2" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="BL2" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="BM2" s="15" t="s">
         <v>86</v>
@@ -1633,11 +1654,11 @@
       <c r="BV2" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="BW2" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="BX2" s="24" t="s">
-        <v>87</v>
+      <c r="BW2" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="BX2" s="15" t="s">
+        <v>86</v>
       </c>
       <c r="BY2" s="24" t="s">
         <v>87</v>
@@ -1669,11 +1690,11 @@
       <c r="CH2" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="CI2" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="CJ2" s="12" t="s">
-        <v>175</v>
+      <c r="CI2" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="CJ2" s="24" t="s">
+        <v>87</v>
       </c>
       <c r="CK2" s="12" t="s">
         <v>175</v>
@@ -1681,8 +1702,14 @@
       <c r="CL2" s="12" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="3" spans="1:90" s="7" customFormat="1" ht="208.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="CM2" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="CN2" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:92" s="7" customFormat="1" ht="208.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>88</v>
       </c>
@@ -1851,110 +1878,116 @@
       <c r="BD3" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="BE3" s="17" t="s">
+      <c r="BE3" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="BF3" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="BF3" s="17" t="s">
+      <c r="BG3" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="BG3" s="17" t="s">
+      <c r="BH3" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="BH3" s="17" t="s">
+      <c r="BI3" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="BI3" s="17" t="s">
+      <c r="BJ3" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="BJ3" s="17" t="s">
+      <c r="BK3" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="BK3" s="15" t="s">
+      <c r="BL3" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="BM3" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="BL3" s="15" t="s">
+      <c r="BN3" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="BM3" s="15" t="s">
+      <c r="BO3" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="BN3" s="15" t="s">
+      <c r="BP3" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="BO3" s="15" t="s">
+      <c r="BQ3" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="BP3" s="15" t="s">
+      <c r="BR3" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="BQ3" s="15" t="s">
+      <c r="BS3" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="BR3" s="15" t="s">
+      <c r="BT3" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="BS3" s="15" t="s">
+      <c r="BU3" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="BT3" s="15" t="s">
+      <c r="BV3" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="BU3" s="15" t="s">
+      <c r="BW3" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="BV3" s="15" t="s">
+      <c r="BX3" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="BW3" s="24" t="s">
+      <c r="BY3" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="BX3" s="24" t="s">
+      <c r="BZ3" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="BY3" s="24" t="s">
+      <c r="CA3" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="BZ3" s="24" t="s">
+      <c r="CB3" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="CA3" s="24" t="s">
+      <c r="CC3" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="CB3" s="24" t="s">
+      <c r="CD3" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="CC3" s="24" t="s">
+      <c r="CE3" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="CD3" s="24" t="s">
+      <c r="CF3" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="CE3" s="24" t="s">
+      <c r="CG3" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="CF3" s="24" t="s">
+      <c r="CH3" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="CG3" s="24" t="s">
+      <c r="CI3" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="CH3" s="24" t="s">
+      <c r="CJ3" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="CI3" s="12" t="s">
+      <c r="CK3" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="CJ3" s="12" t="s">
+      <c r="CL3" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="CK3" s="12" t="s">
+      <c r="CM3" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="CL3" s="12" t="s">
+      <c r="CN3" s="12" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="4" spans="1:90" s="7" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:92" s="7" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>125</v>
       </c>
@@ -2110,7 +2143,7 @@
         <v>131</v>
       </c>
       <c r="BA4" s="19" t="s">
-        <v>133</v>
+        <v>195</v>
       </c>
       <c r="BB4" s="19" t="s">
         <v>131</v>
@@ -2121,26 +2154,30 @@
       <c r="BD4" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="BE4" s="17" t="s">
+      <c r="BE4" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="BF4" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="BF4" s="17" t="s">
+      <c r="BG4" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="BG4" s="17" t="s">
-        <v>133</v>
-      </c>
       <c r="BH4" s="17" t="s">
-        <v>131</v>
+        <v>195</v>
       </c>
       <c r="BI4" s="17" t="s">
         <v>131</v>
       </c>
       <c r="BJ4" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="BK4" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="BK4" s="15"/>
-      <c r="BL4" s="15"/>
+      <c r="BL4" s="17" t="s">
+        <v>193</v>
+      </c>
       <c r="BM4" s="15"/>
       <c r="BN4" s="15"/>
       <c r="BO4" s="15"/>
@@ -2151,8 +2188,8 @@
       <c r="BT4" s="15"/>
       <c r="BU4" s="15"/>
       <c r="BV4" s="15"/>
-      <c r="BW4" s="24"/>
-      <c r="BX4" s="24"/>
+      <c r="BW4" s="15"/>
+      <c r="BX4" s="15"/>
       <c r="BY4" s="24"/>
       <c r="BZ4" s="24"/>
       <c r="CA4" s="24"/>
@@ -2163,14 +2200,14 @@
       <c r="CF4" s="24"/>
       <c r="CG4" s="24"/>
       <c r="CH4" s="24"/>
-      <c r="CI4" s="12"/>
-      <c r="CJ4" s="12"/>
+      <c r="CI4" s="24"/>
+      <c r="CJ4" s="24"/>
       <c r="CK4" s="12"/>
       <c r="CL4" s="12"/>
-    </row>
-    <row r="5" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="BK5" s="15"/>
-      <c r="BL5" s="15"/>
+      <c r="CM4" s="12"/>
+      <c r="CN4" s="12"/>
+    </row>
+    <row r="5" spans="1:92" x14ac:dyDescent="0.25">
       <c r="BM5" s="15"/>
       <c r="BN5" s="15"/>
       <c r="BO5" s="15"/>
@@ -2181,8 +2218,8 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="15"/>
-      <c r="BW5" s="24"/>
-      <c r="BX5" s="24"/>
+      <c r="BW5" s="15"/>
+      <c r="BX5" s="15"/>
       <c r="BY5" s="24"/>
       <c r="BZ5" s="24"/>
       <c r="CA5" s="24"/>
@@ -2193,10 +2230,10 @@
       <c r="CF5" s="24"/>
       <c r="CG5" s="24"/>
       <c r="CH5" s="24"/>
-    </row>
-    <row r="6" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="BK6" s="15"/>
-      <c r="BL6" s="15"/>
+      <c r="CI5" s="24"/>
+      <c r="CJ5" s="24"/>
+    </row>
+    <row r="6" spans="1:92" x14ac:dyDescent="0.25">
       <c r="BM6" s="15"/>
       <c r="BN6" s="15"/>
       <c r="BO6" s="15"/>
@@ -2207,8 +2244,8 @@
       <c r="BT6" s="15"/>
       <c r="BU6" s="15"/>
       <c r="BV6" s="15"/>
-      <c r="BW6" s="24"/>
-      <c r="BX6" s="24"/>
+      <c r="BW6" s="15"/>
+      <c r="BX6" s="15"/>
       <c r="BY6" s="24"/>
       <c r="BZ6" s="24"/>
       <c r="CA6" s="24"/>
@@ -2219,6 +2256,8 @@
       <c r="CF6" s="24"/>
       <c r="CG6" s="24"/>
       <c r="CH6" s="24"/>
+      <c r="CI6" s="24"/>
+      <c r="CJ6" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_PH2_FEB26.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_PH2_FEB26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gary.cheng_cn\Projects\itm-evaluation-dashboard\dashboard-ui\src\components\Research\variables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18AE0F1E-76EB-4715-8CDA-4F34878ABB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA93DB29-8ACA-42E6-B942-804BC9BADFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="270" windowWidth="19290" windowHeight="11730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32610" yWindow="2235" windowWidth="25185" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RQ8" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="247">
   <si>
     <t>Variables</t>
   </si>
@@ -769,6 +769,24 @@
   </si>
   <si>
     <t>Number of times this patient's required injuries were treated correctly for the first time</t>
+  </si>
+  <si>
+    <t>Urban Patient{N}_dragged</t>
+  </si>
+  <si>
+    <t>Whether patient {N} was dragged at any point or not</t>
+  </si>
+  <si>
+    <t>Yes/No</t>
+  </si>
+  <si>
+    <t>0 = No evac, 1 = Round 1 evac, 2 = Round 2 evac</t>
+  </si>
+  <si>
+    <t>0 = No evac, 1 = Round 1 evac, 2 = Round 2 eva</t>
+  </si>
+  <si>
+    <t>Desert Patient{N}_dragged</t>
   </si>
 </sst>
 </file>
@@ -1254,7 +1272,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:DR6"/>
+  <dimension ref="A1:DT6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="16.7265625" style="6" bestFit="1" customWidth="1"/>
@@ -1275,32 +1293,32 @@
     <col min="54" max="61" width="16.7265625" style="18" customWidth="1"/>
     <col min="62" max="66" width="13" style="18" bestFit="1" customWidth="1"/>
     <col min="67" max="72" width="13" style="20" bestFit="1" customWidth="1"/>
-    <col min="73" max="80" width="13" style="20" customWidth="1"/>
-    <col min="81" max="86" width="13" style="18" bestFit="1" customWidth="1"/>
-    <col min="87" max="94" width="13" style="18" customWidth="1"/>
-    <col min="95" max="95" width="87.7265625" style="16" customWidth="1"/>
-    <col min="96" max="97" width="73" style="16" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="38.54296875" style="14" customWidth="1"/>
-    <col min="99" max="99" width="34.7265625" style="14" customWidth="1"/>
-    <col min="100" max="100" width="73" style="16" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="32.54296875" style="14" customWidth="1"/>
-    <col min="102" max="106" width="32.26953125" style="14" customWidth="1"/>
-    <col min="107" max="107" width="87.7265625" style="25" customWidth="1"/>
-    <col min="108" max="109" width="73" style="25" bestFit="1" customWidth="1"/>
-    <col min="110" max="110" width="38.54296875" style="23" customWidth="1"/>
-    <col min="111" max="111" width="34.7265625" style="23" customWidth="1"/>
-    <col min="112" max="112" width="73" style="25" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="87.7265625" style="25" customWidth="1"/>
-    <col min="114" max="115" width="73" style="25" bestFit="1" customWidth="1"/>
-    <col min="116" max="116" width="38.54296875" style="23" customWidth="1"/>
-    <col min="117" max="117" width="34.7265625" style="23" customWidth="1"/>
-    <col min="118" max="118" width="73" style="25" bestFit="1" customWidth="1"/>
-    <col min="119" max="119" width="14.7265625" style="13" customWidth="1"/>
-    <col min="120" max="120" width="15.26953125" style="13" customWidth="1"/>
-    <col min="121" max="122" width="9.1796875" style="13"/>
+    <col min="73" max="81" width="13" style="20" customWidth="1"/>
+    <col min="82" max="87" width="13" style="18" bestFit="1" customWidth="1"/>
+    <col min="88" max="96" width="13" style="18" customWidth="1"/>
+    <col min="97" max="97" width="87.7265625" style="16" customWidth="1"/>
+    <col min="98" max="99" width="73" style="16" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="38.54296875" style="14" customWidth="1"/>
+    <col min="101" max="101" width="34.7265625" style="14" customWidth="1"/>
+    <col min="102" max="102" width="73" style="16" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="32.54296875" style="14" customWidth="1"/>
+    <col min="104" max="108" width="32.26953125" style="14" customWidth="1"/>
+    <col min="109" max="109" width="87.7265625" style="25" customWidth="1"/>
+    <col min="110" max="111" width="73" style="25" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="38.54296875" style="23" customWidth="1"/>
+    <col min="113" max="113" width="34.7265625" style="23" customWidth="1"/>
+    <col min="114" max="114" width="73" style="25" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="87.7265625" style="25" customWidth="1"/>
+    <col min="116" max="117" width="73" style="25" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="38.54296875" style="23" customWidth="1"/>
+    <col min="119" max="119" width="34.7265625" style="23" customWidth="1"/>
+    <col min="120" max="120" width="73" style="25" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="14.7265625" style="13" customWidth="1"/>
+    <col min="122" max="122" width="15.26953125" style="13" customWidth="1"/>
+    <col min="123" max="124" width="9.1796875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:122" s="7" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:124" s="7" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1518,157 +1536,163 @@
         <v>51</v>
       </c>
       <c r="BU1" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="BV1" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="BV1" s="19" t="s">
+      <c r="BW1" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="BW1" s="19" t="s">
+      <c r="BX1" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="BX1" s="19" t="s">
+      <c r="BY1" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="BY1" s="19" t="s">
+      <c r="BZ1" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="BZ1" s="19" t="s">
+      <c r="CA1" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="CA1" s="19" t="s">
+      <c r="CB1" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="CB1" s="19" t="s">
+      <c r="CC1" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="CC1" s="17" t="s">
+      <c r="CD1" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="CD1" s="17" t="s">
+      <c r="CE1" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="CE1" s="17" t="s">
+      <c r="CF1" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="CF1" s="17" t="s">
+      <c r="CG1" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="CG1" s="17" t="s">
+      <c r="CH1" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="CH1" s="17" t="s">
+      <c r="CI1" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="CI1" s="17" t="s">
+      <c r="CJ1" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="CK1" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="CJ1" s="17" t="s">
+      <c r="CL1" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="CK1" s="17" t="s">
+      <c r="CM1" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="CL1" s="17" t="s">
+      <c r="CN1" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="CM1" s="17" t="s">
+      <c r="CO1" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="CN1" s="17" t="s">
+      <c r="CP1" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="CO1" s="17" t="s">
+      <c r="CQ1" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="CP1" s="17" t="s">
+      <c r="CR1" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="CQ1" s="14" t="s">
+      <c r="CS1" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="CR1" s="14" t="s">
+      <c r="CT1" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="CS1" s="14" t="s">
+      <c r="CU1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="CT1" s="14" t="s">
+      <c r="CV1" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="CU1" s="14" t="s">
+      <c r="CW1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="CV1" s="14" t="s">
+      <c r="CX1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="CW1" s="14" t="s">
+      <c r="CY1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="CX1" s="14" t="s">
+      <c r="CZ1" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="CY1" s="14" t="s">
+      <c r="DA1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="CZ1" s="14" t="s">
+      <c r="DB1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="DA1" s="14" t="s">
+      <c r="DC1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="DB1" s="14" t="s">
+      <c r="DD1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="DC1" s="23" t="s">
+      <c r="DE1" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="DD1" s="23" t="s">
+      <c r="DF1" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="DE1" s="23" t="s">
+      <c r="DG1" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="DF1" s="23" t="s">
+      <c r="DH1" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="DG1" s="23" t="s">
+      <c r="DI1" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="DH1" s="23" t="s">
+      <c r="DJ1" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="DI1" s="23" t="s">
+      <c r="DK1" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="DJ1" s="23" t="s">
+      <c r="DL1" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="DK1" s="23" t="s">
+      <c r="DM1" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="DL1" s="23" t="s">
+      <c r="DN1" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="DM1" s="23" t="s">
+      <c r="DO1" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="DN1" s="23" t="s">
+      <c r="DP1" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="DO1" s="12" t="s">
+      <c r="DQ1" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="DP1" s="12" t="s">
+      <c r="DR1" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="DQ1" s="12" t="s">
+      <c r="DS1" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="DR1" s="12" t="s">
+      <c r="DT1" s="12" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:122" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:124" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>82</v>
       </c>
@@ -1909,7 +1933,7 @@
       <c r="CB2" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="CC2" s="17" t="s">
+      <c r="CC2" s="19" t="s">
         <v>85</v>
       </c>
       <c r="CD2" s="17" t="s">
@@ -1951,11 +1975,11 @@
       <c r="CP2" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="CQ2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="CR2" s="15" t="s">
-        <v>86</v>
+      <c r="CQ2" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="CR2" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="CS2" s="15" t="s">
         <v>86</v>
@@ -1987,11 +2011,11 @@
       <c r="DB2" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="DC2" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="DD2" s="24" t="s">
-        <v>87</v>
+      <c r="DC2" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="DD2" s="15" t="s">
+        <v>86</v>
       </c>
       <c r="DE2" s="24" t="s">
         <v>87</v>
@@ -2023,11 +2047,11 @@
       <c r="DN2" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="DO2" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="DP2" s="12" t="s">
-        <v>175</v>
+      <c r="DO2" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="DP2" s="24" t="s">
+        <v>87</v>
       </c>
       <c r="DQ2" s="12" t="s">
         <v>175</v>
@@ -2035,8 +2059,14 @@
       <c r="DR2" s="12" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="3" spans="1:122" s="7" customFormat="1" ht="299" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="DS2" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="DT2" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:124" s="7" customFormat="1" ht="299" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>88</v>
       </c>
@@ -2254,157 +2284,163 @@
         <v>112</v>
       </c>
       <c r="BU3" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="BV3" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="BV3" s="19" t="s">
+      <c r="BW3" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="BW3" s="19" t="s">
+      <c r="BX3" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="BX3" s="19" t="s">
+      <c r="BY3" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="BY3" s="19" t="s">
+      <c r="BZ3" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="BZ3" s="19" t="s">
+      <c r="CA3" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="CA3" s="19" t="s">
+      <c r="CB3" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="CB3" s="19" t="s">
+      <c r="CC3" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="CC3" s="17" t="s">
+      <c r="CD3" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="CD3" s="17" t="s">
+      <c r="CE3" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="CE3" s="17" t="s">
+      <c r="CF3" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="CF3" s="17" t="s">
+      <c r="CG3" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="CG3" s="17" t="s">
+      <c r="CH3" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="CH3" s="17" t="s">
+      <c r="CI3" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="CI3" s="17" t="s">
+      <c r="CJ3" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="CK3" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="CJ3" s="17" t="s">
+      <c r="CL3" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="CK3" s="17" t="s">
+      <c r="CM3" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="CL3" s="17" t="s">
+      <c r="CN3" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="CM3" s="17" t="s">
+      <c r="CO3" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="CN3" s="17" t="s">
+      <c r="CP3" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="CO3" s="17" t="s">
+      <c r="CQ3" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="CP3" s="17" t="s">
+      <c r="CR3" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="CQ3" s="15" t="s">
+      <c r="CS3" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="CR3" s="15" t="s">
+      <c r="CT3" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="CS3" s="15" t="s">
+      <c r="CU3" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="CT3" s="15" t="s">
+      <c r="CV3" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="CU3" s="15" t="s">
+      <c r="CW3" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="CV3" s="15" t="s">
+      <c r="CX3" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="CW3" s="15" t="s">
+      <c r="CY3" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="CX3" s="15" t="s">
+      <c r="CZ3" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="CY3" s="15" t="s">
+      <c r="DA3" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="CZ3" s="15" t="s">
+      <c r="DB3" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="DA3" s="15" t="s">
+      <c r="DC3" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="DB3" s="15" t="s">
+      <c r="DD3" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="DC3" s="24" t="s">
+      <c r="DE3" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="DD3" s="24" t="s">
+      <c r="DF3" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="DE3" s="24" t="s">
+      <c r="DG3" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="DF3" s="24" t="s">
+      <c r="DH3" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="DG3" s="24" t="s">
+      <c r="DI3" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="DH3" s="24" t="s">
+      <c r="DJ3" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="DI3" s="24" t="s">
+      <c r="DK3" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="DJ3" s="24" t="s">
+      <c r="DL3" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="DK3" s="24" t="s">
+      <c r="DM3" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="DL3" s="24" t="s">
+      <c r="DN3" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="DM3" s="24" t="s">
+      <c r="DO3" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="DN3" s="24" t="s">
+      <c r="DP3" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="DO3" s="12" t="s">
+      <c r="DQ3" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="DP3" s="12" t="s">
+      <c r="DR3" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="DQ3" s="12" t="s">
+      <c r="DS3" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="DR3" s="12" t="s">
+      <c r="DT3" s="12" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="4" spans="1:122" s="7" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:124" s="7" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>125</v>
       </c>
@@ -2608,7 +2644,7 @@
         <v>131</v>
       </c>
       <c r="BQ4" s="19" t="s">
-        <v>133</v>
+        <v>245</v>
       </c>
       <c r="BR4" s="19" t="s">
         <v>131</v>
@@ -2620,7 +2656,7 @@
         <v>135</v>
       </c>
       <c r="BU4" s="19" t="s">
-        <v>131</v>
+        <v>243</v>
       </c>
       <c r="BV4" s="19" t="s">
         <v>131</v>
@@ -2643,29 +2679,29 @@
       <c r="CB4" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="CC4" s="17" t="s">
+      <c r="CC4" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="CD4" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="CD4" s="17" t="s">
+      <c r="CE4" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="CE4" s="17" t="s">
-        <v>133</v>
-      </c>
       <c r="CF4" s="17" t="s">
-        <v>131</v>
+        <v>244</v>
       </c>
       <c r="CG4" s="17" t="s">
         <v>131</v>
       </c>
       <c r="CH4" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="CI4" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="CI4" s="17" t="s">
-        <v>131</v>
-      </c>
       <c r="CJ4" s="17" t="s">
-        <v>131</v>
+        <v>243</v>
       </c>
       <c r="CK4" s="17" t="s">
         <v>131</v>
@@ -2685,8 +2721,12 @@
       <c r="CP4" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="CQ4" s="15"/>
-      <c r="CR4" s="15"/>
+      <c r="CQ4" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="CR4" s="17" t="s">
+        <v>131</v>
+      </c>
       <c r="CS4" s="15"/>
       <c r="CT4" s="15"/>
       <c r="CU4" s="15"/>
@@ -2697,8 +2737,8 @@
       <c r="CZ4" s="15"/>
       <c r="DA4" s="15"/>
       <c r="DB4" s="15"/>
-      <c r="DC4" s="24"/>
-      <c r="DD4" s="24"/>
+      <c r="DC4" s="15"/>
+      <c r="DD4" s="15"/>
       <c r="DE4" s="24"/>
       <c r="DF4" s="24"/>
       <c r="DG4" s="24"/>
@@ -2709,14 +2749,14 @@
       <c r="DL4" s="24"/>
       <c r="DM4" s="24"/>
       <c r="DN4" s="24"/>
-      <c r="DO4" s="12"/>
-      <c r="DP4" s="12"/>
+      <c r="DO4" s="24"/>
+      <c r="DP4" s="24"/>
       <c r="DQ4" s="12"/>
       <c r="DR4" s="12"/>
-    </row>
-    <row r="5" spans="1:122" x14ac:dyDescent="0.35">
-      <c r="CQ5" s="15"/>
-      <c r="CR5" s="15"/>
+      <c r="DS4" s="12"/>
+      <c r="DT4" s="12"/>
+    </row>
+    <row r="5" spans="1:124" x14ac:dyDescent="0.35">
       <c r="CS5" s="15"/>
       <c r="CT5" s="15"/>
       <c r="CU5" s="15"/>
@@ -2727,8 +2767,8 @@
       <c r="CZ5" s="15"/>
       <c r="DA5" s="15"/>
       <c r="DB5" s="15"/>
-      <c r="DC5" s="24"/>
-      <c r="DD5" s="24"/>
+      <c r="DC5" s="15"/>
+      <c r="DD5" s="15"/>
       <c r="DE5" s="24"/>
       <c r="DF5" s="24"/>
       <c r="DG5" s="24"/>
@@ -2739,10 +2779,10 @@
       <c r="DL5" s="24"/>
       <c r="DM5" s="24"/>
       <c r="DN5" s="24"/>
-    </row>
-    <row r="6" spans="1:122" x14ac:dyDescent="0.35">
-      <c r="CQ6" s="15"/>
-      <c r="CR6" s="15"/>
+      <c r="DO5" s="24"/>
+      <c r="DP5" s="24"/>
+    </row>
+    <row r="6" spans="1:124" x14ac:dyDescent="0.35">
       <c r="CS6" s="15"/>
       <c r="CT6" s="15"/>
       <c r="CU6" s="15"/>
@@ -2753,8 +2793,8 @@
       <c r="CZ6" s="15"/>
       <c r="DA6" s="15"/>
       <c r="DB6" s="15"/>
-      <c r="DC6" s="24"/>
-      <c r="DD6" s="24"/>
+      <c r="DC6" s="15"/>
+      <c r="DD6" s="15"/>
       <c r="DE6" s="24"/>
       <c r="DF6" s="24"/>
       <c r="DG6" s="24"/>
@@ -2765,6 +2805,8 @@
       <c r="DL6" s="24"/>
       <c r="DM6" s="24"/>
       <c r="DN6" s="24"/>
+      <c r="DO6" s="24"/>
+      <c r="DP6" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_PH2_FEB26.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_PH2_FEB26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gary.cheng_cn\Projects\itm-evaluation-dashboard\dashboard-ui\src\components\Research\variables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA93DB29-8ACA-42E6-B942-804BC9BADFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19627CB-3096-450F-B3B2-EB78EF77F622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32610" yWindow="2235" windowWidth="25185" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RQ8" sheetId="1" r:id="rId1"/>
@@ -214,9 +214,6 @@
     <t>Urban Patient{N}_tag</t>
   </si>
   <si>
-    <t>AF_Intercept_Text</t>
-  </si>
-  <si>
     <t>AF_medical_Text</t>
   </si>
   <si>
@@ -250,9 +247,6 @@
     <t>SS_attribute_Text</t>
   </si>
   <si>
-    <t>AF_Intercept_Desert</t>
-  </si>
-  <si>
     <t>AF_medical_Desert</t>
   </si>
   <si>
@@ -266,9 +260,6 @@
   </si>
   <si>
     <t>MF_attribute_Desert</t>
-  </si>
-  <si>
-    <t>AF_Intercept_Urban</t>
   </si>
   <si>
     <t>AF_medical_Urban</t>
@@ -787,6 +778,15 @@
   </si>
   <si>
     <t>Desert Patient{N}_dragged</t>
+  </si>
+  <si>
+    <t>AF_intercept_Desert</t>
+  </si>
+  <si>
+    <t>AF_intercept_Text</t>
+  </si>
+  <si>
+    <t>AF_intercept_Urban</t>
   </si>
 </sst>
 </file>
@@ -1329,10 +1329,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F1" s="19" t="s">
         <v>3</v>
@@ -1365,10 +1365,10 @@
         <v>12</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="Q1" s="19" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="R1" s="17" t="s">
         <v>13</v>
@@ -1428,28 +1428,28 @@
         <v>31</v>
       </c>
       <c r="AK1" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="AL1" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM1" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="AN1" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="AL1" s="19" t="s">
+      <c r="AO1" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="AM1" s="19" t="s">
+      <c r="AP1" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="AN1" s="19" t="s">
+      <c r="AQ1" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="AO1" s="19" t="s">
+      <c r="AR1" s="19" t="s">
         <v>195</v>
-      </c>
-      <c r="AP1" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="AQ1" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="AR1" s="19" t="s">
-        <v>198</v>
       </c>
       <c r="AS1" s="19" t="s">
         <v>32</v>
@@ -1479,28 +1479,28 @@
         <v>40</v>
       </c>
       <c r="BB1" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="BC1" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="BD1" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="BE1" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="BC1" s="17" t="s">
+      <c r="BF1" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="BD1" s="17" t="s">
+      <c r="BG1" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="BE1" s="17" t="s">
+      <c r="BH1" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="BF1" s="17" t="s">
+      <c r="BI1" s="17" t="s">
         <v>203</v>
-      </c>
-      <c r="BG1" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="BH1" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="BI1" s="17" t="s">
-        <v>206</v>
       </c>
       <c r="BJ1" s="17" t="s">
         <v>41</v>
@@ -1536,31 +1536,31 @@
         <v>51</v>
       </c>
       <c r="BU1" s="19" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="BV1" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="BW1" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="BX1" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="BY1" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="BW1" s="19" t="s">
+      <c r="BZ1" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="BX1" s="19" t="s">
+      <c r="CA1" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="BY1" s="19" t="s">
+      <c r="CB1" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="BZ1" s="19" t="s">
+      <c r="CC1" s="19" t="s">
         <v>211</v>
-      </c>
-      <c r="CA1" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="CB1" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="CC1" s="19" t="s">
-        <v>214</v>
       </c>
       <c r="CD1" s="17" t="s">
         <v>52</v>
@@ -1581,1151 +1581,1151 @@
         <v>57</v>
       </c>
       <c r="CJ1" s="17" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="CK1" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="CL1" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="CM1" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="CN1" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="CL1" s="17" t="s">
+      <c r="CO1" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="CM1" s="17" t="s">
+      <c r="CP1" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="CN1" s="17" t="s">
+      <c r="CQ1" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="CO1" s="17" t="s">
+      <c r="CR1" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="CP1" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="CQ1" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="CR1" s="17" t="s">
-        <v>222</v>
-      </c>
       <c r="CS1" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="CT1" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="CT1" s="14" t="s">
+      <c r="CU1" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="CU1" s="14" t="s">
+      <c r="CV1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="CV1" s="14" t="s">
+      <c r="CW1" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="CW1" s="14" t="s">
+      <c r="CX1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="CX1" s="14" t="s">
+      <c r="CY1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="CY1" s="14" t="s">
+      <c r="CZ1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="CZ1" s="14" t="s">
+      <c r="DA1" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="DA1" s="14" t="s">
+      <c r="DB1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="DB1" s="14" t="s">
+      <c r="DC1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="DC1" s="14" t="s">
+      <c r="DD1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="DD1" s="14" t="s">
+      <c r="DE1" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="DF1" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="DE1" s="23" t="s">
+      <c r="DG1" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="DF1" s="23" t="s">
+      <c r="DH1" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="DG1" s="23" t="s">
+      <c r="DI1" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="DH1" s="23" t="s">
+      <c r="DJ1" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="DI1" s="23" t="s">
+      <c r="DK1" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="DL1" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="DJ1" s="23" t="s">
+      <c r="DM1" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="DK1" s="23" t="s">
+      <c r="DN1" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="DL1" s="23" t="s">
+      <c r="DO1" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="DM1" s="23" t="s">
+      <c r="DP1" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="DN1" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="DO1" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="DP1" s="23" t="s">
-        <v>81</v>
-      </c>
       <c r="DQ1" s="12" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="DR1" s="12" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="DS1" s="12" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="DT1" s="12" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:124" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="E2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="S2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="T2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="U2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="V2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="W2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="X2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AR2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AW2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AX2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AY2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AZ2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BA2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BB2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BC2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BE2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BF2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BG2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BH2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BI2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BJ2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BK2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BL2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BM2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BN2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="BP2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="BQ2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="BR2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="BS2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="BT2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="BU2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="BV2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="BW2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="BX2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="BY2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="BZ2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="CA2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="CB2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="CC2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="CD2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CE2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CF2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CG2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CH2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CI2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CJ2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CK2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CL2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CM2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CN2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CO2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CP2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CQ2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CR2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="CS2" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="CT2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="CU2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="CV2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="CW2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="CX2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="CY2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="CZ2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="DA2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="DB2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="DC2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="DD2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="DE2" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="M2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="O2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="P2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="R2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="S2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="T2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="U2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="V2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="W2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="X2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AC2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="AE2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="AF2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="AG2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AM2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AP2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AR2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AU2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AV2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AW2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="AZ2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BA2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BB2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BC2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BD2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BE2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BF2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BG2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BH2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BI2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BJ2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BK2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BL2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BM2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BN2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="BO2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="BP2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="BQ2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="BR2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="BS2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="BT2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="BU2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="BV2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="BW2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="BX2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="BY2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="BZ2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="CA2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="CB2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="CC2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="CD2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CE2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CF2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CG2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CH2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CI2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CJ2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CK2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CL2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CM2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CN2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CO2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CP2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CQ2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CR2" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="CS2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="CT2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="CU2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="CV2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="CW2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="CX2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="CY2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="CZ2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="DA2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="DB2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="DC2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="DD2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="DE2" s="24" t="s">
-        <v>87</v>
-      </c>
       <c r="DF2" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="DG2" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="DH2" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="DI2" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="DJ2" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="DK2" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="DL2" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="DM2" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="DN2" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="DO2" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="DP2" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="DQ2" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="DR2" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="DS2" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="DT2" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:124" s="7" customFormat="1" ht="299" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F3" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="G3" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="L3" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="M3" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="N3" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="F3" s="19" t="s">
+      <c r="O3" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="P3" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q3" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="R3" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="S3" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="T3" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="I3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="L3" s="19" t="s">
+      <c r="U3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="V3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="W3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="X3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z3" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA3" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="AB3" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC3" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD3" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="N3" s="19" t="s">
+      <c r="AE3" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="O3" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="P3" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="R3" s="17" t="s">
+      <c r="AF3" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="S3" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="T3" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="U3" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="V3" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="W3" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="X3" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y3" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z3" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA3" s="19" t="s">
+      <c r="AG3" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="AB3" s="19" t="s">
+      <c r="AH3" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="AC3" s="19" t="s">
+      <c r="AI3" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="AD3" s="17" t="s">
+      <c r="AJ3" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK3" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="AL3" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="AM3" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="AN3" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="AO3" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="AP3" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="AQ3" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="AR3" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="AS3" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AT3" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AU3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="AV3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="AW3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="AX3" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="AE3" s="17" t="s">
+      <c r="AY3" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="AF3" s="17" t="s">
+      <c r="AZ3" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AG3" s="19" t="s">
+      <c r="BA3" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="AH3" s="19" t="s">
+      <c r="BB3" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="BC3" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="BD3" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="BE3" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="BF3" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="BG3" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="BH3" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="BI3" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="BJ3" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="AI3" s="19" t="s">
+      <c r="BK3" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="AJ3" s="19" t="s">
+      <c r="BL3" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="AK3" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="AL3" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="AM3" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="AN3" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="AO3" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="AP3" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="AQ3" s="19" t="s">
+      <c r="BM3" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="BN3" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="BO3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="BP3" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="BQ3" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="BR3" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="BS3" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BT3" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="BU3" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="BV3" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="AR3" s="19" t="s">
+      <c r="BW3" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="BX3" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="AS3" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="AT3" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="AU3" s="19" t="s">
+      <c r="BY3" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="BZ3" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="CA3" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="CB3" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="CC3" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="CD3" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="AV3" s="19" t="s">
+      <c r="CE3" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="AW3" s="19" t="s">
+      <c r="CF3" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="AX3" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="AY3" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="AZ3" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="BA3" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="BB3" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="BC3" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="BD3" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="BE3" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="BF3" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="BG3" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="BH3" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="BI3" s="17" t="s">
+      <c r="CG3" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="CH3" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="CI3" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="CJ3" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="CK3" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="CL3" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="BJ3" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="BK3" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="BL3" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="BM3" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="BN3" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="BO3" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="BP3" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BQ3" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="BR3" s="19" t="s">
+      <c r="CM3" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="CN3" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="CO3" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="CP3" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="CQ3" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="CR3" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="CS3" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="BS3" s="19" t="s">
+      <c r="CT3" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="BT3" s="19" t="s">
+      <c r="CU3" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="BU3" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="BV3" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="BW3" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="BX3" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="BY3" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="BZ3" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="CA3" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="CB3" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="CC3" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="CD3" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="CE3" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="CF3" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="CG3" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="CH3" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="CI3" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="CJ3" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="CK3" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="CL3" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="CM3" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="CN3" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="CO3" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="CP3" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="CQ3" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="CR3" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="CS3" s="15" t="s">
+      <c r="CV3" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="CT3" s="15" t="s">
+      <c r="CW3" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="CU3" s="15" t="s">
+      <c r="CX3" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="CV3" s="15" t="s">
+      <c r="CY3" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="CW3" s="15" t="s">
+      <c r="CZ3" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="CX3" s="15" t="s">
+      <c r="DA3" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="CY3" s="15" t="s">
+      <c r="DB3" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="CZ3" s="15" t="s">
+      <c r="DC3" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="DA3" s="15" t="s">
+      <c r="DD3" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="DB3" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="DC3" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="DD3" s="15" t="s">
-        <v>124</v>
-      </c>
       <c r="DE3" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="DF3" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="DG3" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="DH3" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="DF3" s="24" t="s">
+      <c r="DI3" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="DG3" s="24" t="s">
+      <c r="DJ3" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="DH3" s="24" t="s">
+      <c r="DK3" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="DL3" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="DI3" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="DJ3" s="24" t="s">
+      <c r="DM3" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="DN3" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="DO3" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="DP3" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="DQ3" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="DR3" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="DS3" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="DK3" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="DL3" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="DM3" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="DN3" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="DO3" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="DP3" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="DQ3" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="DR3" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="DS3" s="12" t="s">
+      <c r="DT3" s="12" t="s">
         <v>176</v>
-      </c>
-      <c r="DT3" s="12" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:124" s="7" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="N4" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="O4" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="P4" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q4" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="R4" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="S4" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="U4" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="V4" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="W4" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="X4" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y4" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z4" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA4" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB4" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F4" s="19" t="s">
+      <c r="AC4" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="AD4" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE4" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF4" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="AG4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AL4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AN4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AO4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS4" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="AT4" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="AU4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AV4" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="AW4" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AX4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="AZ4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BA4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BB4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BC4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BG4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BH4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BJ4" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="BK4" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="L4" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="M4" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="N4" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="O4" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="P4" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q4" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="R4" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="S4" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="T4" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="U4" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="V4" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="W4" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="X4" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y4" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z4" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="AA4" s="19" t="s">
+      <c r="BL4" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="AB4" s="19" t="s">
+      <c r="BM4" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="AC4" s="19" t="s">
+      <c r="BN4" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="AD4" s="17" t="s">
+      <c r="BO4" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="BP4" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="AE4" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="AF4" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="AG4" s="19" t="s">
+      <c r="BQ4" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="BR4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT4" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="BU4" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="BV4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BW4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BX4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CB4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CC4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD4" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="AH4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="AI4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="AJ4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="AK4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="AL4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="AM4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="AN4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="AO4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="AP4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="AR4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="AS4" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="AT4" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="AU4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV4" s="19" t="s">
+      <c r="CE4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF4" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="CG4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI4" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="AW4" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="AX4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="AY4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="AZ4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="BA4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="BB4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="BC4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="BD4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="BE4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="BF4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="BG4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="BH4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="BI4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="BJ4" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="BK4" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="BL4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="BM4" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="BN4" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="BO4" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="BP4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="BQ4" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="BR4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="BS4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="BT4" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="BU4" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="BV4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="BW4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="BX4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="BY4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="BZ4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="CA4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="CB4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="CC4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="CD4" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="CE4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="CF4" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="CG4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="CH4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="CI4" s="17" t="s">
-        <v>135</v>
-      </c>
       <c r="CJ4" s="17" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="CK4" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="CL4" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="CM4" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="CN4" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="CO4" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="CP4" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="CQ4" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="CR4" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="CS4" s="15"/>
       <c r="CT4" s="15"/>
@@ -2832,136 +2832,136 @@
   <sheetData>
     <row r="1" spans="1:6" s="11" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2"/>
@@ -10918,136 +10918,136 @@
   <sheetData>
     <row r="1" spans="1:6" s="11" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2"/>

--- a/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_PH2_FEB26.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_PH2_FEB26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gary.cheng_cn\Projects\itm-evaluation-dashboard\dashboard-ui\src\components\Research\variables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19627CB-3096-450F-B3B2-EB78EF77F622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3007A490-1C20-49BB-A52A-EC2DF11EB12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RQ8" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="249">
   <si>
     <t>Variables</t>
   </si>
@@ -659,9 +659,6 @@
   </si>
   <si>
     <t>Desert Patient{N}_treat_repeat_hits_required</t>
-  </si>
-  <si>
-    <t>Desert Patient[{N}_treat_repeat_false_alarms_required</t>
   </si>
   <si>
     <t>Desert Patient{N}_treat_hits_w_supp</t>
@@ -787,6 +784,15 @@
   </si>
   <si>
     <t>AF_intercept_Urban</t>
+  </si>
+  <si>
+    <t>Desert Patient{N}_treat_repeat_false_alarms_required</t>
+  </si>
+  <si>
+    <t>Urban Probe_PS1_Actions</t>
+  </si>
+  <si>
+    <t>List of moderator buttons the participant selected in response to the initial personal-safety inject</t>
   </si>
 </sst>
 </file>
@@ -1272,7 +1278,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:DT6"/>
+  <dimension ref="A1:DU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="16.7265625" style="6" bestFit="1" customWidth="1"/>
@@ -1284,41 +1290,42 @@
     <col min="18" max="23" width="12.453125" style="18" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="13" style="18" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="12.453125" style="18" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="16.7265625" style="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="16.7265625" style="18" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="16.7265625" style="20" bestFit="1" customWidth="1"/>
-    <col min="36" max="44" width="16.7265625" style="20" customWidth="1"/>
-    <col min="45" max="49" width="13" style="20" bestFit="1" customWidth="1"/>
-    <col min="50" max="53" width="16.7265625" style="18" bestFit="1" customWidth="1"/>
-    <col min="54" max="61" width="16.7265625" style="18" customWidth="1"/>
-    <col min="62" max="66" width="13" style="18" bestFit="1" customWidth="1"/>
-    <col min="67" max="72" width="13" style="20" bestFit="1" customWidth="1"/>
-    <col min="73" max="81" width="13" style="20" customWidth="1"/>
-    <col min="82" max="87" width="13" style="18" bestFit="1" customWidth="1"/>
-    <col min="88" max="96" width="13" style="18" customWidth="1"/>
-    <col min="97" max="97" width="87.7265625" style="16" customWidth="1"/>
-    <col min="98" max="99" width="73" style="16" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="38.54296875" style="14" customWidth="1"/>
-    <col min="101" max="101" width="34.7265625" style="14" customWidth="1"/>
-    <col min="102" max="102" width="73" style="16" bestFit="1" customWidth="1"/>
-    <col min="103" max="103" width="32.54296875" style="14" customWidth="1"/>
-    <col min="104" max="108" width="32.26953125" style="14" customWidth="1"/>
-    <col min="109" max="109" width="87.7265625" style="25" customWidth="1"/>
-    <col min="110" max="111" width="73" style="25" bestFit="1" customWidth="1"/>
-    <col min="112" max="112" width="38.54296875" style="23" customWidth="1"/>
-    <col min="113" max="113" width="34.7265625" style="23" customWidth="1"/>
-    <col min="114" max="114" width="73" style="25" bestFit="1" customWidth="1"/>
-    <col min="115" max="115" width="87.7265625" style="25" customWidth="1"/>
-    <col min="116" max="117" width="73" style="25" bestFit="1" customWidth="1"/>
-    <col min="118" max="118" width="38.54296875" style="23" customWidth="1"/>
-    <col min="119" max="119" width="34.7265625" style="23" customWidth="1"/>
-    <col min="120" max="120" width="73" style="25" bestFit="1" customWidth="1"/>
-    <col min="121" max="121" width="14.7265625" style="13" customWidth="1"/>
-    <col min="122" max="122" width="15.26953125" style="13" customWidth="1"/>
-    <col min="123" max="124" width="9.1796875" style="13"/>
+    <col min="27" max="27" width="12.453125" style="18" customWidth="1"/>
+    <col min="28" max="30" width="16.7265625" style="20" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="16.7265625" style="18" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="16.7265625" style="20" bestFit="1" customWidth="1"/>
+    <col min="37" max="45" width="16.7265625" style="20" customWidth="1"/>
+    <col min="46" max="50" width="13" style="20" bestFit="1" customWidth="1"/>
+    <col min="51" max="54" width="16.7265625" style="18" bestFit="1" customWidth="1"/>
+    <col min="55" max="62" width="16.7265625" style="18" customWidth="1"/>
+    <col min="63" max="67" width="13" style="18" bestFit="1" customWidth="1"/>
+    <col min="68" max="73" width="13" style="20" bestFit="1" customWidth="1"/>
+    <col min="74" max="82" width="13" style="20" customWidth="1"/>
+    <col min="83" max="88" width="13" style="18" bestFit="1" customWidth="1"/>
+    <col min="89" max="97" width="13" style="18" customWidth="1"/>
+    <col min="98" max="98" width="87.7265625" style="16" customWidth="1"/>
+    <col min="99" max="100" width="73" style="16" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="38.54296875" style="14" customWidth="1"/>
+    <col min="102" max="102" width="34.7265625" style="14" customWidth="1"/>
+    <col min="103" max="103" width="73" style="16" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="32.54296875" style="14" customWidth="1"/>
+    <col min="105" max="109" width="32.26953125" style="14" customWidth="1"/>
+    <col min="110" max="110" width="87.7265625" style="25" customWidth="1"/>
+    <col min="111" max="112" width="73" style="25" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="38.54296875" style="23" customWidth="1"/>
+    <col min="114" max="114" width="34.7265625" style="23" customWidth="1"/>
+    <col min="115" max="115" width="73" style="25" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="87.7265625" style="25" customWidth="1"/>
+    <col min="117" max="118" width="73" style="25" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="38.54296875" style="23" customWidth="1"/>
+    <col min="120" max="120" width="34.7265625" style="23" customWidth="1"/>
+    <col min="121" max="121" width="73" style="25" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="14.7265625" style="13" customWidth="1"/>
+    <col min="123" max="123" width="15.26953125" style="13" customWidth="1"/>
+    <col min="124" max="125" width="9.1796875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" s="7" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:125" s="7" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1397,302 +1404,305 @@
       <c r="Z1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="19" t="s">
+      <c r="AA1" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB1" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="19" t="s">
+      <c r="AC1" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="AC1" s="19" t="s">
+      <c r="AD1" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="AD1" s="17" t="s">
+      <c r="AE1" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AE1" s="17" t="s">
+      <c r="AF1" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="AF1" s="17" t="s">
+      <c r="AG1" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="AG1" s="19" t="s">
+      <c r="AH1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="AH1" s="19" t="s">
+      <c r="AI1" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="AI1" s="19" t="s">
+      <c r="AJ1" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="AJ1" s="19" t="s">
+      <c r="AK1" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="AK1" s="19" t="s">
+      <c r="AL1" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="AL1" s="19" t="s">
+      <c r="AM1" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="AM1" s="19" t="s">
+      <c r="AN1" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="AN1" s="19" t="s">
+      <c r="AO1" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="AO1" s="19" t="s">
+      <c r="AP1" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="AP1" s="19" t="s">
+      <c r="AQ1" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="AQ1" s="19" t="s">
+      <c r="AR1" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="AR1" s="19" t="s">
+      <c r="AS1" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="AS1" s="19" t="s">
+      <c r="AT1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="AT1" s="19" t="s">
+      <c r="AU1" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AU1" s="19" t="s">
+      <c r="AV1" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="AV1" s="19" t="s">
+      <c r="AW1" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="AW1" s="19" t="s">
+      <c r="AX1" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="AX1" s="17" t="s">
+      <c r="AY1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="AY1" s="17" t="s">
+      <c r="AZ1" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="AZ1" s="17" t="s">
+      <c r="BA1" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="BA1" s="17" t="s">
+      <c r="BB1" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="BB1" s="17" t="s">
+      <c r="BC1" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="BC1" s="17" t="s">
+      <c r="BD1" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="BD1" s="17" t="s">
+      <c r="BE1" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="BE1" s="17" t="s">
+      <c r="BF1" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="BF1" s="17" t="s">
+      <c r="BG1" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="BG1" s="17" t="s">
+      <c r="BH1" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="BH1" s="17" t="s">
+      <c r="BI1" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="BI1" s="17" t="s">
+      <c r="BJ1" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="BJ1" s="17" t="s">
+      <c r="BK1" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="BK1" s="17" t="s">
+      <c r="BL1" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="BL1" s="17" t="s">
+      <c r="BM1" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="BM1" s="17" t="s">
+      <c r="BN1" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="BN1" s="17" t="s">
+      <c r="BO1" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="BO1" s="19" t="s">
+      <c r="BP1" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="BP1" s="19" t="s">
+      <c r="BQ1" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="BQ1" s="19" t="s">
+      <c r="BR1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="BR1" s="19" t="s">
+      <c r="BS1" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="BS1" s="19" t="s">
+      <c r="BT1" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="BT1" s="19" t="s">
+      <c r="BU1" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="BU1" s="19" t="s">
+      <c r="BV1" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="BW1" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="BX1" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="BY1" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="BZ1" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="CA1" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="CB1" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="CC1" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="CD1" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="CE1" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="CF1" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="CG1" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="CH1" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="CI1" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="CJ1" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="CK1" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="CL1" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="CM1" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="CN1" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="CO1" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="CP1" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="CQ1" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="CR1" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="CS1" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="CT1" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="CU1" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="CV1" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="CW1" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="CX1" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="CY1" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="CZ1" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="DA1" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="DB1" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="DC1" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="DD1" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="DE1" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="DF1" s="23" t="s">
         <v>243</v>
       </c>
-      <c r="BV1" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="BW1" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="BX1" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="BY1" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="BZ1" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="CA1" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="CB1" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="CC1" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="CD1" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="CE1" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="CF1" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="CG1" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="CH1" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="CI1" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="CJ1" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="CK1" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="CL1" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="CM1" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="CN1" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="CO1" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="CP1" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="CQ1" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="CR1" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="CS1" s="14" t="s">
+      <c r="DG1" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="DH1" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="DI1" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="DJ1" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="DK1" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="DL1" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="CT1" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="CU1" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="CV1" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="CW1" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="CX1" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="CY1" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="CZ1" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="DA1" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="DB1" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="DC1" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="DD1" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="DE1" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="DF1" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="DG1" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="DH1" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="DI1" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="DJ1" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="DK1" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="DL1" s="23" t="s">
+      <c r="DM1" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="DM1" s="23" t="s">
+      <c r="DN1" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="DN1" s="23" t="s">
+      <c r="DO1" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="DO1" s="23" t="s">
+      <c r="DP1" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="DP1" s="23" t="s">
+      <c r="DQ1" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="DQ1" s="12" t="s">
+      <c r="DR1" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="DR1" s="12" t="s">
+      <c r="DS1" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="DS1" s="12" t="s">
+      <c r="DT1" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="DT1" s="12" t="s">
+      <c r="DU1" s="12" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:124" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:125" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>79</v>
       </c>
@@ -1771,7 +1781,7 @@
       <c r="Z2" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="AA2" s="19" t="s">
+      <c r="AA2" s="17" t="s">
         <v>82</v>
       </c>
       <c r="AB2" s="19" t="s">
@@ -1780,7 +1790,7 @@
       <c r="AC2" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="AD2" s="17" t="s">
+      <c r="AD2" s="19" t="s">
         <v>82</v>
       </c>
       <c r="AE2" s="17" t="s">
@@ -1789,7 +1799,7 @@
       <c r="AF2" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="AG2" s="19" t="s">
+      <c r="AG2" s="17" t="s">
         <v>82</v>
       </c>
       <c r="AH2" s="19" t="s">
@@ -1840,7 +1850,7 @@
       <c r="AW2" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="AX2" s="17" t="s">
+      <c r="AX2" s="19" t="s">
         <v>82</v>
       </c>
       <c r="AY2" s="17" t="s">
@@ -1891,7 +1901,7 @@
       <c r="BN2" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="BO2" s="19" t="s">
+      <c r="BO2" s="17" t="s">
         <v>82</v>
       </c>
       <c r="BP2" s="19" t="s">
@@ -1936,7 +1946,7 @@
       <c r="CC2" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="CD2" s="17" t="s">
+      <c r="CD2" s="19" t="s">
         <v>82</v>
       </c>
       <c r="CE2" s="17" t="s">
@@ -1981,8 +1991,8 @@
       <c r="CR2" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="CS2" s="15" t="s">
-        <v>83</v>
+      <c r="CS2" s="17" t="s">
+        <v>82</v>
       </c>
       <c r="CT2" s="15" t="s">
         <v>83</v>
@@ -2017,8 +2027,8 @@
       <c r="DD2" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="DE2" s="24" t="s">
-        <v>84</v>
+      <c r="DE2" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="DF2" s="24" t="s">
         <v>84</v>
@@ -2053,8 +2063,8 @@
       <c r="DP2" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="DQ2" s="12" t="s">
-        <v>172</v>
+      <c r="DQ2" s="24" t="s">
+        <v>84</v>
       </c>
       <c r="DR2" s="12" t="s">
         <v>172</v>
@@ -2065,8 +2075,11 @@
       <c r="DT2" s="12" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="3" spans="1:124" s="7" customFormat="1" ht="299" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="DU2" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:125" s="7" customFormat="1" ht="299" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>85</v>
       </c>
@@ -2145,41 +2158,41 @@
       <c r="Z3" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="AA3" s="19" t="s">
+      <c r="AA3" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB3" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AB3" s="19" t="s">
+      <c r="AC3" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="AC3" s="19" t="s">
+      <c r="AD3" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="AD3" s="17" t="s">
+      <c r="AE3" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="AE3" s="17" t="s">
+      <c r="AF3" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="AF3" s="17" t="s">
+      <c r="AG3" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="AG3" s="19" t="s">
+      <c r="AH3" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="AH3" s="19" t="s">
+      <c r="AI3" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="AI3" s="19" t="s">
+      <c r="AJ3" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="AJ3" s="19" t="s">
+      <c r="AK3" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="AK3" s="19" t="s">
-        <v>220</v>
-      </c>
       <c r="AL3" s="19" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="AM3" s="19" t="s">
         <v>222</v>
@@ -2188,49 +2201,49 @@
         <v>221</v>
       </c>
       <c r="AO3" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="AP3" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ3" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="AP3" s="19" t="s">
+      <c r="AR3" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="AQ3" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="AR3" s="19" t="s">
-        <v>228</v>
-      </c>
       <c r="AS3" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="AT3" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="AT3" s="19" t="s">
+      <c r="AU3" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="AU3" s="19" t="s">
+      <c r="AV3" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="AV3" s="19" t="s">
+      <c r="AW3" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="AW3" s="19" t="s">
+      <c r="AX3" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="AX3" s="17" t="s">
+      <c r="AY3" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="AY3" s="17" t="s">
+      <c r="AZ3" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="AZ3" s="17" t="s">
+      <c r="BA3" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="BA3" s="17" t="s">
+      <c r="BB3" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="BB3" s="17" t="s">
-        <v>220</v>
-      </c>
       <c r="BC3" s="17" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="BD3" s="17" t="s">
         <v>222</v>
@@ -2239,208 +2252,211 @@
         <v>221</v>
       </c>
       <c r="BF3" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="BG3" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="BH3" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="BG3" s="17" t="s">
+      <c r="BI3" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="BH3" s="17" t="s">
+      <c r="BJ3" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="BI3" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="BJ3" s="17" t="s">
+      <c r="BK3" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BK3" s="17" t="s">
+      <c r="BL3" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="BL3" s="17" t="s">
+      <c r="BM3" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="BM3" s="17" t="s">
+      <c r="BN3" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="BN3" s="17" t="s">
+      <c r="BO3" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="BO3" s="19" t="s">
+      <c r="BP3" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="BP3" s="19" t="s">
+      <c r="BQ3" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="BQ3" s="19" t="s">
+      <c r="BR3" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="BR3" s="19" t="s">
+      <c r="BS3" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="BS3" s="19" t="s">
+      <c r="BT3" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="BT3" s="19" t="s">
+      <c r="BU3" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="BU3" s="19" t="s">
-        <v>239</v>
-      </c>
       <c r="BV3" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="BW3" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="BX3" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="BW3" s="19" t="s">
+      <c r="BY3" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="BX3" s="19" t="s">
+      <c r="BZ3" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="BY3" s="19" t="s">
+      <c r="CA3" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="BZ3" s="19" t="s">
+      <c r="CB3" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="CA3" s="19" t="s">
+      <c r="CC3" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="CB3" s="19" t="s">
+      <c r="CD3" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="CC3" s="19" t="s">
+      <c r="CE3" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="CF3" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="CG3" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="CH3" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="CI3" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="CJ3" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="CK3" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="CL3" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="CD3" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="CE3" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="CF3" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="CG3" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="CH3" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="CI3" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="CJ3" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="CK3" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="CL3" s="17" t="s">
+      <c r="CM3" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="CN3" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="CM3" s="17" t="s">
+      <c r="CO3" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="CN3" s="17" t="s">
+      <c r="CP3" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="CO3" s="17" t="s">
+      <c r="CQ3" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="CP3" s="17" t="s">
+      <c r="CR3" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="CQ3" s="17" t="s">
+      <c r="CS3" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="CR3" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="CS3" s="15" t="s">
+      <c r="CT3" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="CT3" s="15" t="s">
+      <c r="CU3" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="CU3" s="15" t="s">
+      <c r="CV3" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="CV3" s="15" t="s">
+      <c r="CW3" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="CW3" s="15" t="s">
+      <c r="CX3" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="CX3" s="15" t="s">
+      <c r="CY3" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="CY3" s="15" t="s">
+      <c r="CZ3" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="CZ3" s="15" t="s">
+      <c r="DA3" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="DA3" s="15" t="s">
+      <c r="DB3" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="DB3" s="15" t="s">
+      <c r="DC3" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="DC3" s="15" t="s">
+      <c r="DD3" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="DD3" s="15" t="s">
+      <c r="DE3" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="DE3" s="24" t="s">
+      <c r="DF3" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="DF3" s="24" t="s">
+      <c r="DG3" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="DG3" s="24" t="s">
+      <c r="DH3" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="DH3" s="24" t="s">
+      <c r="DI3" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="DI3" s="24" t="s">
+      <c r="DJ3" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="DJ3" s="24" t="s">
+      <c r="DK3" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="DK3" s="24" t="s">
+      <c r="DL3" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="DL3" s="24" t="s">
+      <c r="DM3" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="DM3" s="24" t="s">
+      <c r="DN3" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="DN3" s="24" t="s">
+      <c r="DO3" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="DO3" s="24" t="s">
+      <c r="DP3" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="DP3" s="24" t="s">
+      <c r="DQ3" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="DQ3" s="12" t="s">
+      <c r="DR3" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="DR3" s="12" t="s">
+      <c r="DS3" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="DS3" s="12" t="s">
+      <c r="DT3" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="DT3" s="12" t="s">
+      <c r="DU3" s="12" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="4" spans="1:124" s="7" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:125" s="7" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>122</v>
       </c>
@@ -2517,26 +2533,26 @@
       <c r="Z4" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="AA4" s="19" t="s">
+      <c r="AA4" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB4" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="AB4" s="19" t="s">
+      <c r="AC4" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="AC4" s="19" t="s">
+      <c r="AD4" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="AD4" s="17" t="s">
+      <c r="AE4" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="AE4" s="17" t="s">
+      <c r="AF4" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="AF4" s="17" t="s">
+      <c r="AG4" s="17" t="s">
         <v>127</v>
-      </c>
-      <c r="AG4" s="19" t="s">
-        <v>128</v>
       </c>
       <c r="AH4" s="19" t="s">
         <v>128</v>
@@ -2572,22 +2588,22 @@
         <v>128</v>
       </c>
       <c r="AS4" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AT4" s="19" t="s">
         <v>127</v>
       </c>
       <c r="AU4" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="AV4" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="AV4" s="19" t="s">
+      <c r="AW4" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="AW4" s="19" t="s">
+      <c r="AX4" s="19" t="s">
         <v>130</v>
-      </c>
-      <c r="AX4" s="17" t="s">
-        <v>128</v>
       </c>
       <c r="AY4" s="17" t="s">
         <v>128</v>
@@ -2623,43 +2639,43 @@
         <v>128</v>
       </c>
       <c r="BJ4" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK4" s="17" t="s">
         <v>127</v>
       </c>
       <c r="BL4" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="BM4" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="BM4" s="17" t="s">
+      <c r="BN4" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="BN4" s="17" t="s">
+      <c r="BO4" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="BO4" s="19" t="s">
+      <c r="BP4" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="BP4" s="19" t="s">
+      <c r="BQ4" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="BQ4" s="19" t="s">
-        <v>242</v>
-      </c>
       <c r="BR4" s="19" t="s">
-        <v>128</v>
+        <v>241</v>
       </c>
       <c r="BS4" s="19" t="s">
         <v>128</v>
       </c>
       <c r="BT4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU4" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="BU4" s="19" t="s">
-        <v>240</v>
-      </c>
       <c r="BV4" s="19" t="s">
-        <v>128</v>
+        <v>239</v>
       </c>
       <c r="BW4" s="19" t="s">
         <v>128</v>
@@ -2682,29 +2698,29 @@
       <c r="CC4" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="CD4" s="17" t="s">
+      <c r="CD4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CE4" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="CE4" s="17" t="s">
+      <c r="CF4" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="CF4" s="17" t="s">
-        <v>241</v>
-      </c>
       <c r="CG4" s="17" t="s">
-        <v>128</v>
+        <v>240</v>
       </c>
       <c r="CH4" s="17" t="s">
         <v>128</v>
       </c>
       <c r="CI4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="CJ4" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="CJ4" s="17" t="s">
-        <v>240</v>
-      </c>
       <c r="CK4" s="17" t="s">
-        <v>128</v>
+        <v>239</v>
       </c>
       <c r="CL4" s="17" t="s">
         <v>128</v>
@@ -2727,7 +2743,9 @@
       <c r="CR4" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="CS4" s="15"/>
+      <c r="CS4" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="CT4" s="15"/>
       <c r="CU4" s="15"/>
       <c r="CV4" s="15"/>
@@ -2739,7 +2757,7 @@
       <c r="DB4" s="15"/>
       <c r="DC4" s="15"/>
       <c r="DD4" s="15"/>
-      <c r="DE4" s="24"/>
+      <c r="DE4" s="15"/>
       <c r="DF4" s="24"/>
       <c r="DG4" s="24"/>
       <c r="DH4" s="24"/>
@@ -2751,13 +2769,13 @@
       <c r="DN4" s="24"/>
       <c r="DO4" s="24"/>
       <c r="DP4" s="24"/>
-      <c r="DQ4" s="12"/>
+      <c r="DQ4" s="24"/>
       <c r="DR4" s="12"/>
       <c r="DS4" s="12"/>
       <c r="DT4" s="12"/>
-    </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.35">
-      <c r="CS5" s="15"/>
+      <c r="DU4" s="12"/>
+    </row>
+    <row r="5" spans="1:125" x14ac:dyDescent="0.35">
       <c r="CT5" s="15"/>
       <c r="CU5" s="15"/>
       <c r="CV5" s="15"/>
@@ -2769,7 +2787,7 @@
       <c r="DB5" s="15"/>
       <c r="DC5" s="15"/>
       <c r="DD5" s="15"/>
-      <c r="DE5" s="24"/>
+      <c r="DE5" s="15"/>
       <c r="DF5" s="24"/>
       <c r="DG5" s="24"/>
       <c r="DH5" s="24"/>
@@ -2781,9 +2799,9 @@
       <c r="DN5" s="24"/>
       <c r="DO5" s="24"/>
       <c r="DP5" s="24"/>
-    </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.35">
-      <c r="CS6" s="15"/>
+      <c r="DQ5" s="24"/>
+    </row>
+    <row r="6" spans="1:125" x14ac:dyDescent="0.35">
       <c r="CT6" s="15"/>
       <c r="CU6" s="15"/>
       <c r="CV6" s="15"/>
@@ -2795,7 +2813,7 @@
       <c r="DB6" s="15"/>
       <c r="DC6" s="15"/>
       <c r="DD6" s="15"/>
-      <c r="DE6" s="24"/>
+      <c r="DE6" s="15"/>
       <c r="DF6" s="24"/>
       <c r="DG6" s="24"/>
       <c r="DH6" s="24"/>
@@ -2807,6 +2825,7 @@
       <c r="DN6" s="24"/>
       <c r="DO6" s="24"/>
       <c r="DP6" s="24"/>
+      <c r="DQ6" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
